--- a/public/sample_uploads/investors.xlsx
+++ b/public/sample_uploads/investors.xlsx
@@ -128,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t xml:space="preserve">Name *</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t xml:space="preserve">Category *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector</t>
   </si>
   <si>
     <t xml:space="preserve">City</t>
@@ -368,28 +371,32 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -644,139 +651,147 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="9.47265625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="16.85"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="3" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0"/>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
